--- a/_I_SecoveljskeSoline/phenodata_20230306.xlsx
+++ b/_I_SecoveljskeSoline/phenodata_20230306.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\DEJAVNOSTI\OMIKE\pISA-Projects\_p_ExtAnalysis\_I_SecoveljskeSoline\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markop\Documents\GitHub\AlKoSol\_I_SecoveljskeSoline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFE72414-A706-4690-BB61-D6E0A895CC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB666761-860C-41EB-9F7C-D6E7E4ECE027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,9 +164,6 @@
     <t>Sample_number_in_batch</t>
   </si>
   <si>
-    <t>O:\DEJAVNOSTI\OMIKE\pISA-Projects\_p_ExtAnalysis\_I_SecoveljskeSoline\_S_DNA_seq\_A_01-gDNAisol</t>
-  </si>
-  <si>
     <t>Isolation_info_files_location</t>
   </si>
   <si>
@@ -396,6 +393,9 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>.\_I_SecoveljskeSoline\_S_DNA_seq\_A_01-gDNAisol</t>
   </si>
 </sst>
 </file>
@@ -523,9 +523,6 @@
   </cellStyles>
   <dxfs count="10">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -553,6 +550,9 @@
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -572,16 +572,16 @@
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{9AAA9FE1-A7DF-4D1B-AC80-F693A92AE4A3}" name="SampleID"/>
     <tableColumn id="2" xr3:uid="{8DD626E9-3639-407E-915A-6342493FFAB2}" name="Sample_name"/>
-    <tableColumn id="13" xr3:uid="{CB10FF36-1423-4513-8BF1-FAA130F410E4}" name="Sample_Figure_label" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{44594B30-16E8-4FEB-B268-6C3AB58A9802}" name="Date_of_sampling" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{0F7FA423-3C18-4863-AE3A-9E1A1BD2A373}" name="Sampling_month" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{990FB1FE-64E7-4FCD-9AD3-B6530A5D0A3C}" name="Season" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{926D22AD-1C25-4F61-85B9-B1D6C2BCDBCC}" name="Batch_number" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{2F92F6A1-1E84-407F-A7B1-96B30F895B12}" name="Sample_number_in_batch" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{043D5A34-1057-4C31-A3E0-01F98AFC823F}" name="Brine_salinity(Be)" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{57C8C22B-8F07-4EAB-BDC5-9C4BECCD7064}" name="Brine_Temperature(C)" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{A071CCEE-8327-4BBC-A2B0-A5C85865FE55}" name="DNA_isolation_date" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{094A65FD-0D15-41F6-AC0A-93DF5467F350}" name="Storage" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{CB10FF36-1423-4513-8BF1-FAA130F410E4}" name="Sample_Figure_label" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{44594B30-16E8-4FEB-B268-6C3AB58A9802}" name="Date_of_sampling" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{0F7FA423-3C18-4863-AE3A-9E1A1BD2A373}" name="Sampling_month" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{990FB1FE-64E7-4FCD-9AD3-B6530A5D0A3C}" name="Season" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{926D22AD-1C25-4F61-85B9-B1D6C2BCDBCC}" name="Batch_number" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{2F92F6A1-1E84-407F-A7B1-96B30F895B12}" name="Sample_number_in_batch" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{043D5A34-1057-4C31-A3E0-01F98AFC823F}" name="Brine_salinity(Be)" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{57C8C22B-8F07-4EAB-BDC5-9C4BECCD7064}" name="Brine_Temperature(C)" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{A071CCEE-8327-4BBC-A2B0-A5C85865FE55}" name="DNA_isolation_date" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{094A65FD-0D15-41F6-AC0A-93DF5467F350}" name="Storage" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{7F51C28B-5E09-4248-9CDC-A8A661DE5A20}" name="Isolation_info_files_location"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -876,16 +876,16 @@
         <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D1" t="s">
         <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G1" t="s">
         <v>22</v>
@@ -894,19 +894,19 @@
         <v>41</v>
       </c>
       <c r="I1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" t="s">
         <v>85</v>
-      </c>
-      <c r="J1" t="s">
-        <v>86</v>
       </c>
       <c r="K1" t="s">
         <v>21</v>
       </c>
       <c r="L1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -917,16 +917,16 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D2" s="3">
         <v>20230406</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G2" s="3">
         <v>1</v>
@@ -944,10 +944,10 @@
         <v>20230925</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -958,16 +958,16 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D3" s="3">
         <v>20230406</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
@@ -985,10 +985,10 @@
         <v>20230925</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -999,16 +999,16 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D4" s="3">
         <v>20230406</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G4" s="3">
         <v>1</v>
@@ -1026,10 +1026,10 @@
         <v>20230925</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -1040,16 +1040,16 @@
         <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4">
         <v>20230406</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G5" s="4">
         <v>1</v>
@@ -1067,10 +1067,10 @@
         <v>20230925</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -1081,16 +1081,16 @@
         <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D6" s="5">
         <v>20230523</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -1108,10 +1108,10 @@
         <v>20230925</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -1122,16 +1122,16 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D7" s="3">
         <v>20230523</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" s="3">
         <v>2</v>
@@ -1149,10 +1149,10 @@
         <v>20230925</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -1163,16 +1163,16 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D8" s="3">
         <v>20230523</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G8" s="3">
         <v>2</v>
@@ -1190,10 +1190,10 @@
         <v>20230925</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M8" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -1204,16 +1204,16 @@
         <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D9" s="4">
         <v>20230523</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" s="4">
         <v>2</v>
@@ -1231,10 +1231,10 @@
         <v>20230925</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -1245,16 +1245,16 @@
         <v>31</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D10" s="5">
         <v>20230706</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G10" s="5">
         <v>3</v>
@@ -1272,10 +1272,10 @@
         <v>20230925</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -1286,16 +1286,16 @@
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D11" s="3">
         <v>20230706</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G11" s="3">
         <v>3</v>
@@ -1313,10 +1313,10 @@
         <v>20230925</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M11" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -1327,16 +1327,16 @@
         <v>33</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" s="3">
         <v>20230706</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G12" s="3">
         <v>3</v>
@@ -1354,10 +1354,10 @@
         <v>20230925</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M12" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -1368,16 +1368,16 @@
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3">
         <v>20230706</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G13" s="3">
         <v>3</v>
@@ -1395,10 +1395,10 @@
         <v>20230925</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M13" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -1409,16 +1409,16 @@
         <v>35</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D14" s="4">
         <v>20230706</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G14" s="4">
         <v>3</v>
@@ -1436,10 +1436,10 @@
         <v>20230925</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -1450,16 +1450,16 @@
         <v>36</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D15" s="3">
         <v>20230824</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G15" s="3">
         <v>4</v>
@@ -1477,10 +1477,10 @@
         <v>20230925</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M15" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -1491,16 +1491,16 @@
         <v>37</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D16" s="3">
         <v>20230824</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G16" s="3">
         <v>4</v>
@@ -1518,10 +1518,10 @@
         <v>20230925</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M16" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -1532,16 +1532,16 @@
         <v>38</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D17" s="3">
         <v>20230824</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G17" s="3">
         <v>4</v>
@@ -1559,10 +1559,10 @@
         <v>20230925</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M17" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -1573,16 +1573,16 @@
         <v>39</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D18" s="3">
         <v>20230824</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G18" s="3">
         <v>4</v>
@@ -1600,10 +1600,10 @@
         <v>20230925</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M18" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -1614,16 +1614,16 @@
         <v>40</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D19" s="7">
         <v>20230824</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G19" s="7">
         <v>4</v>
@@ -1641,30 +1641,30 @@
         <v>20230925</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D20" s="3">
         <v>20230921</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G20" s="3">
         <v>5</v>
@@ -1682,30 +1682,30 @@
         <v>20230925</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M20" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D21" s="3">
         <v>20230921</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G21" s="3">
         <v>5</v>
@@ -1723,30 +1723,30 @@
         <v>20230925</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M21" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D22" s="7">
         <v>20230921</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G22" s="7">
         <v>5</v>
@@ -1764,36 +1764,36 @@
         <v>20230925</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" s="3">
         <v>20230824</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G23" s="3">
         <v>4</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I23" s="3">
         <v>29.3</v>
@@ -1805,36 +1805,36 @@
         <v>20231106</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M23" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D24" s="3">
         <v>20230824</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G24" s="3">
         <v>4</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I24" s="3">
         <v>29.3</v>
@@ -1846,36 +1846,36 @@
         <v>20231106</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M24" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D25" s="3">
         <v>20230824</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G25" s="3">
         <v>4</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I25" s="3">
         <v>29.3</v>
@@ -1887,36 +1887,36 @@
         <v>20231106</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M25" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D26" s="3">
         <v>20230824</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G26" s="3">
         <v>4</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I26" s="3">
         <v>29.3</v>
@@ -1928,36 +1928,36 @@
         <v>20231106</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M26" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D27" s="7">
         <v>20230824</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G27" s="7">
         <v>4</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I27" s="7">
         <v>29.3</v>
@@ -1969,36 +1969,36 @@
         <v>20231106</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D28" s="3">
         <v>20230706</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G28" s="3">
         <v>3</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I28" s="3">
         <v>26</v>
@@ -2010,36 +2010,36 @@
         <v>20231107</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M28" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D29" s="3">
         <v>20230706</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G29" s="3">
         <v>3</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I29" s="3">
         <v>26</v>
@@ -2051,36 +2051,36 @@
         <v>20231107</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M29" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D30" s="3">
         <v>20230706</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G30" s="3">
         <v>3</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I30" s="3">
         <v>26</v>
@@ -2092,36 +2092,36 @@
         <v>20231107</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M30" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D31" s="3">
         <v>20230706</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G31" s="3">
         <v>3</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I31" s="3">
         <v>26</v>
@@ -2133,36 +2133,36 @@
         <v>20231107</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M31" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D32" s="7">
         <v>20230706</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G32" s="7">
         <v>3</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I32" s="7">
         <v>26</v>
@@ -2174,30 +2174,30 @@
         <v>20231107</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" t="s">
         <v>62</v>
       </c>
-      <c r="B33" t="s">
-        <v>63</v>
-      </c>
       <c r="C33" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D33" s="13">
         <v>20230921</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G33" s="3">
         <v>5</v>
@@ -2215,30 +2215,30 @@
         <v>20231122</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M33" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="C34" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D34" s="7">
         <v>20230921</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G34" s="7">
         <v>5</v>
@@ -2256,30 +2256,30 @@
         <v>20231122</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" t="s">
         <v>66</v>
       </c>
-      <c r="B35" t="s">
-        <v>67</v>
-      </c>
       <c r="C35" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D35" s="3">
         <v>20230824</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G35" s="3">
         <v>5</v>
@@ -2297,30 +2297,30 @@
         <v>20231122</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M35" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" t="s">
         <v>68</v>
       </c>
-      <c r="B36" t="s">
-        <v>69</v>
-      </c>
       <c r="C36" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D36" s="3">
         <v>20230706</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G36" s="3">
         <v>3</v>
@@ -2338,10 +2338,10 @@
         <v>20231122</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M36" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
